--- a/test-files/gene-name-modifications/numbers-as-gene-name-unrelated-input.xlsx
+++ b/test-files/gene-name-modifications/numbers-as-gene-name-unrelated-input.xlsx
@@ -1,59 +1,47 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10410"/>
-  <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mihir/Documents/GRNsight_mihirsamdarshi/test-files/gene-name-modifications/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0A06ACB-68B1-344B-A359-0133BD8A222E}" xr6:coauthVersionLast="32" xr6:coauthVersionMax="32" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="0" yWindow="440" windowWidth="25600" windowHeight="14160" tabRatio="759" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <workbookPr codeName="ThisWorkbook" autoCompressPictures="false" showInkAnnotation="false"/>
   <sheets>
-    <sheet name="network" sheetId="9" r:id="rId1"/>
+    <sheet name="network" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="125725"/>
-  <extLst>
-    <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{7523E5D3-25F3-A5E0-1632-64F254C22452}">
-      <mx:ArchID Flags="2"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
-  <si>
-    <t>rows genes affected/cols genes controlling</t>
-  </si>
-</sst>
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <numFmts count="1">
+    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+  </numFmts>
+  <fonts count="1">
     <font>
-      <sz val="10"/>
+      <sz val="12"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="10"/>
-      <color theme="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="10"/>
-      <color theme="11"/>
-      <name val="Arial"/>
-      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -73,41 +61,17 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="9">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="9">
-    <cellStyle name="Followed Hyperlink" xfId="2" builtinId="9" hidden="1"/>
-    <cellStyle name="Followed Hyperlink" xfId="4" builtinId="9" hidden="1"/>
-    <cellStyle name="Followed Hyperlink" xfId="6" builtinId="9" hidden="1"/>
-    <cellStyle name="Followed Hyperlink" xfId="8" builtinId="9" hidden="1"/>
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8" hidden="1"/>
-    <cellStyle name="Hyperlink" xfId="3" builtinId="8" hidden="1"/>
-    <cellStyle name="Hyperlink" xfId="5" builtinId="8" hidden="1"/>
-    <cellStyle name="Hyperlink" xfId="7" builtinId="8" hidden="1"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
 </styleSheet>
 </file>
 
@@ -432,13 +396,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:V22"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.15">
-      <c r="A1" t="s">
-        <v>0</v>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>cols regulators/rows targets</v>
       </c>
       <c r="B1">
         <v>1</v>
@@ -504,7 +467,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.15">
+    <row r="2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -572,7 +535,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.15">
+    <row r="3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -640,7 +603,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.15">
+    <row r="4">
       <c r="A4">
         <v>3</v>
       </c>
@@ -708,7 +671,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.15">
+    <row r="5">
       <c r="A5">
         <v>4</v>
       </c>
@@ -776,7 +739,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.15">
+    <row r="6">
       <c r="A6">
         <v>5</v>
       </c>
@@ -844,7 +807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.15">
+    <row r="7">
       <c r="A7">
         <v>6</v>
       </c>
@@ -912,7 +875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.15">
+    <row r="8">
       <c r="A8">
         <v>7</v>
       </c>
@@ -980,7 +943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.15">
+    <row r="9">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1048,7 +1011,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.15">
+    <row r="10">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1116,7 +1079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.15">
+    <row r="11">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1184,7 +1147,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.15">
+    <row r="12">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1252,7 +1215,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.15">
+    <row r="13">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1320,7 +1283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.15">
+    <row r="14">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1388,7 +1351,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.15">
+    <row r="15">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1456,7 +1419,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.15">
+    <row r="16">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1524,7 +1487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.15">
+    <row r="17">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1592,7 +1555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.15">
+    <row r="18">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1660,7 +1623,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.15">
+    <row r="19">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1728,7 +1691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.15">
+    <row r="20">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1796,7 +1759,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.15">
+    <row r="21">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1864,7 +1827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.15">
+    <row r="22">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1933,12 +1896,8 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
-  <extLst>
-    <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
-      <mx:PLV Mode="0" OnePage="0" WScale="0"/>
-    </ext>
-  </extLst>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:V22"/>
+  </ignoredErrors>
 </worksheet>
 </file>